--- a/JsonConverter/ExcelFiles/CommentaryData.xlsx
+++ b/JsonConverter/ExcelFiles/CommentaryData.xlsx
@@ -19,66 +19,249 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="81">
+  <x:si>
+    <x:t>comm_clinch_started_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테이크다운 성공! 상대를 바닥에 눕힙니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단단한 중심으로 테이크다운을 막아냅니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치에서 빠져나와 다시 거리를 벌립니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_clinch_escaped_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_clinch_reversed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundEscapeFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바닥에서 벗어나 다시 일어섭니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEscapeFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmissionEscaped</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmissionSucceeded</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_ground_escaped_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmissionInProgress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초크를 풀어냅니다! 위기에서 빠져나왔어요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>낮게 파고듭니다! 테이크다운을 시도합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchReversed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 주도권이 뒤바뀝니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundEscaped</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchEscaped</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClinchStarted</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownAttempt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownDefended</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownToClinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강한 파운딩이 그대로 적중합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩을 피하며 피해를 막아냅니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownSucceeded</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정확한 타격이 상대에게 꽂힙니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TakedownStarted</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResultType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StrikeMissed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Clinch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ground</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wrestling</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_jab</x:t>
+  </x:si>
   <x:si>
     <x:t>StrikeHit</x:t>
   </x:si>
   <x:si>
+    <x:t>Standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
     <x:t>None</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
     <x:t>잽! 빠르고 경쾌하게 적중합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>WrestlingSituation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CommentaryText</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillUserSide</x:t>
   </x:si>
   <x:si>
     <x:t>comm_jab_hit_01</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_jab</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ResultType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingSituation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
     <x:t>MatchSituation</x:t>
   </x:si>
   <x:si>
-    <x:t>GroundPosition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillUserSide</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CommentaryText</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weight</x:t>
+    <x:t>comm_strike_hit_generic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_ground_strike_hit_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_takedown_started_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격이 허공을 가릅니다! 상대가 잘 피했어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_takedown_defended_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_takedown_succeeded_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_takedown_to_clinch_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테이크다운 공방이 클린치 싸움으로 이어집니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드에서 포지션을 한 단계 끌어올립니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치를 잡았습니다! 가까운 거리에서 압박합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치를 풀어내지 못합니다! 계속 붙잡혀 있어요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_submission_progress_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPositionChangeFailed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포지션 전환을 시도하지만 상대가 막아냅니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_submission_escaped_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탭을 받아냅니다! 완벽한 서브미션 승리입니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_position_change_succeeded_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_ground_strike_missed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_position_change_failed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_strike_missed_generic_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundPositionChangeSucceeded</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_clinch_escape_failed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_ground_escape_failed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일어나려 하지만 상대의 압박에서 벗어나지 못합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크가 깊게 들어갑니다! 위험한 상황이에요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>comm_submission_succeeded_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -859,7 +1042,7 @@
     <x:col min="5" max="5" width="24.71484375" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="23.5703125" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="23.4296875" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="33.14453125" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="56.28515625" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="15.14453125" style="1" customWidth="1"/>
     <x:col min="10" max="10" width="26.54296875" style="1" customWidth="1"/>
     <x:col min="11" max="11" width="23.28515625" style="1" customWidth="1"/>
@@ -871,160 +1054,647 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J4" s="4"/>
     </x:row>
-    <x:row r="5" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="3"/>
-    </x:row>
-    <x:row r="6" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A7" s="5"/>
-      <x:c r="B7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A8" s="5"/>
-      <x:c r="B8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A9" s="5"/>
-      <x:c r="B9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A10" s="5"/>
-      <x:c r="B10" s="5"/>
-    </x:row>
-    <x:row r="11" ht="15.75" customHeight="1"/>
-    <x:row r="12" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6"/>
-      <x:c r="B13" s="6"/>
-    </x:row>
-    <x:row r="14" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A14" s="3"/>
-      <x:c r="B14" s="3"/>
-    </x:row>
-    <x:row r="15" ht="15.75" customHeight="1"/>
-    <x:row r="16" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A17" s="5"/>
-      <x:c r="B17" s="5"/>
-    </x:row>
-    <x:row r="18" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A18" s="5"/>
-      <x:c r="B18" s="5"/>
-    </x:row>
-    <x:row r="19" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A19" s="5"/>
-      <x:c r="B19" s="5"/>
-    </x:row>
-    <x:row r="20" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A20" s="5"/>
-      <x:c r="B20" s="5"/>
-    </x:row>
-    <x:row r="21" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A21" s="5"/>
-      <x:c r="B21" s="5"/>
-    </x:row>
-    <x:row r="22" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A22" s="5"/>
-      <x:c r="B22" s="5"/>
-    </x:row>
-    <x:row r="23" spans="1:2" ht="15.75" customHeight="1">
-      <x:c r="A23" s="5"/>
-      <x:c r="B23" s="5"/>
+    <x:row r="5" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A5" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H5" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I5" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A6" s="3" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H6" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I6" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A7" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H7" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I7" s="1">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A8" s="5" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H8" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I8" s="1">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A9" s="5" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H9" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I9" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A10" s="5" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H10" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A11" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H11" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I11" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A12" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H12" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I12" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A13" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H13" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I13" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A14" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H14" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A15" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H15" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I15" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A16" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H16" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I16" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A17" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B17" s="5" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H17" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I17" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A18" s="5" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H18" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I18" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A19" s="5" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B19" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H19" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I19" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A20" s="5" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B20" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H20" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I20" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A21" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H21" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I21" s="1">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A22" s="5" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B22" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H22" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I22" s="1">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A23" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B23" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I23" s="1">
+        <x:v>100</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" spans="1:2" ht="15.75" customHeight="1">
       <x:c r="A24" s="5"/>
